--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18450,6 +18450,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B787" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C787" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D787" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E787" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F787" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G787" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18473,6 +18473,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B788" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C788" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D788" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E788" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G788" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18496,6 +18496,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B789" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C789" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="D789" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E789" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F789" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="G789" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18519,6 +18519,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B790" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C790" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D790" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E790" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="G790" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18360,22 +18360,22 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B783" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C783" t="n">
-        <v>0.990000009536743</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="D783" t="n">
-        <v>0.990000009536743</v>
+        <v>1</v>
       </c>
       <c r="E783" t="n">
-        <v>0.990000009536743</v>
+        <v>1</v>
       </c>
       <c r="F783" t="n">
-        <v>0.990000009536743</v>
+        <v>1.00999999046326</v>
       </c>
       <c r="G783" t="s">
         <v>7</v>
@@ -18383,22 +18383,22 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B784" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="C784" t="n">
-        <v>1</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="D784" t="n">
-        <v>1</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="E784" t="n">
-        <v>1</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="F784" t="n">
-        <v>1</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="G784" t="s">
         <v>7</v>
@@ -18406,10 +18406,10 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B785" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C785" t="n">
         <v>1</v>
@@ -18429,22 +18429,22 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B786" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C786" t="n">
-        <v>0.990000009536743</v>
+        <v>1</v>
       </c>
       <c r="D786" t="n">
-        <v>0.980000019073486</v>
+        <v>1</v>
       </c>
       <c r="E786" t="n">
-        <v>0.980000019073486</v>
+        <v>1</v>
       </c>
       <c r="F786" t="n">
-        <v>0.990000009536743</v>
+        <v>1</v>
       </c>
       <c r="G786" t="s">
         <v>7</v>
@@ -18452,19 +18452,19 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B787" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C787" t="n">
         <v>0.990000009536743</v>
       </c>
       <c r="D787" t="n">
-        <v>0.990000009536743</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="E787" t="n">
-        <v>0.990000009536743</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="F787" t="n">
         <v>0.990000009536743</v>
@@ -18475,22 +18475,22 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B788" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C788" t="n">
-        <v>0.980000019073486</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="D788" t="n">
-        <v>0.959999978542328</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="E788" t="n">
-        <v>0.959999978542328</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="F788" t="n">
-        <v>0.980000019073486</v>
+        <v>0.990000009536743</v>
       </c>
       <c r="G788" t="s">
         <v>7</v>
@@ -18498,13 +18498,13 @@
     </row>
     <row r="789">
       <c r="A789" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B789" t="n">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="C789" t="n">
-        <v>0.975000023841858</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="D789" t="n">
         <v>0.959999978542328</v>
@@ -18513,7 +18513,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="F789" t="n">
-        <v>0.970000028610229</v>
+        <v>0.980000019073486</v>
       </c>
       <c r="G789" t="s">
         <v>7</v>
@@ -18521,24 +18521,47 @@
     </row>
     <row r="790">
       <c r="A790" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B790" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="C790" t="n">
-        <v>0.970000028610229</v>
+        <v>0.975000023841858</v>
       </c>
       <c r="D790" t="n">
-        <v>0.970000028610229</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="E790" t="n">
-        <v>0.970000028610229</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="F790" t="n">
         <v>0.970000028610229</v>
       </c>
       <c r="G790" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B791" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C791" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D791" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E791" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F791" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="G791" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18544,24 +18544,47 @@
     </row>
     <row r="791">
       <c r="A791" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B791" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="C791" t="n">
         <v>0.970000028610229</v>
       </c>
       <c r="D791" t="n">
-        <v>0.949999988079071</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="E791" t="n">
-        <v>0.949999988079071</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="F791" t="n">
         <v>0.970000028610229</v>
       </c>
       <c r="G791" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C792" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D792" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E792" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="G792" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -21019,6 +21019,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B795" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C795" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="D795" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E795" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="F795" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="G795" t="n">
+        <v>0.935000002384186</v>
+      </c>
+      <c r="H795" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -21045,6 +21045,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B796" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C796" t="n">
+        <v>1</v>
+      </c>
+      <c r="D796" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="E796" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G796" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="H796" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18680,6 +18680,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B797" t="n">
+        <v>0</v>
+      </c>
+      <c r="C797" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D797" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E797" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G797" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B798" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C798" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D798" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E798" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="F798"/>
+      <c r="G798" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -21149,6 +21149,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B800" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C800" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D800" t="n">
+        <v>1</v>
+      </c>
+      <c r="E800" t="n">
+        <v>1</v>
+      </c>
+      <c r="F800" t="n">
+        <v>1</v>
+      </c>
+      <c r="G800" t="n">
+        <v>1</v>
+      </c>
+      <c r="H800" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18834,8 +18834,31 @@
       <c r="E803" t="n">
         <v>0.970000028610229</v>
       </c>
-      <c r="F803"/>
+      <c r="F803" t="n">
+        <v>0.949999988079071</v>
+      </c>
       <c r="G803" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B804" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C804" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D804" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E804" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F804"/>
+      <c r="G804" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18857,8 +18857,31 @@
       <c r="E804" t="n">
         <v>0.949999988079071</v>
       </c>
-      <c r="F804"/>
+      <c r="F804" t="n">
+        <v>0.980000019073486</v>
+      </c>
       <c r="G804" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C805" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="D805" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E805" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="F805"/>
+      <c r="G805" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18880,8 +18880,31 @@
       <c r="E805" t="n">
         <v>0.975000023841858</v>
       </c>
-      <c r="F805"/>
+      <c r="F805" t="n">
+        <v>0.970000028610229</v>
+      </c>
       <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C806" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="D806" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E806" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="F806"/>
+      <c r="G806" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18903,8 +18903,31 @@
       <c r="E806" t="n">
         <v>0.970000028610229</v>
       </c>
-      <c r="F806"/>
+      <c r="F806" t="n">
+        <v>0.970000028610229</v>
+      </c>
       <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C807" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D807" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E807" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F807"/>
+      <c r="G807" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -18933,6 +18933,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C808" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D808" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E808" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F808" t="n">
+        <v>0.954999983310699</v>
+      </c>
+      <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -21435,6 +21435,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C811" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="D811" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E811" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F811" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G811" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="H811" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -21461,6 +21461,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B812" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C812" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D812" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E812" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G812" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="H812" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -23926,6 +23926,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="813">
+      <c r="A813" t="s">
+        <v>9</v>
+      </c>
+      <c r="B813" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C813" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="D813" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="E813" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F813" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G813" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="H813" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I813" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="s">
+        <v>9</v>
+      </c>
+      <c r="B814" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C814" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="E814" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="G814" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="H814" t="n">
+        <v>52000</v>
+      </c>
+      <c r="I814" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -23984,6 +23984,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" t="s">
+        <v>9</v>
+      </c>
+      <c r="B815" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C815" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0.925000011920929</v>
+      </c>
+      <c r="E815" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="G815" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="H815" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24013,6 +24013,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" t="s">
+        <v>9</v>
+      </c>
+      <c r="B816" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C816" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E816" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="G816" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="H816" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I816" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24042,6 +24042,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="s">
+        <v>9</v>
+      </c>
+      <c r="B817" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C817" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D817" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="E817" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G817" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H817" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I817" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24071,6 +24071,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C818" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D818" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E818" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="G818" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="H818" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24100,6 +24100,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C819" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="D819" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="E819" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="F819" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G819" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H819" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24114,7 +24114,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="E819" t="n">
-        <v>0.865000009536743</v>
+        <v>0.860000014305115</v>
       </c>
       <c r="F819" t="n">
         <v>0.860000014305115</v>
@@ -24126,6 +24126,35 @@
         <v>12000</v>
       </c>
       <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="s">
+        <v>9</v>
+      </c>
+      <c r="B820" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C820" t="n">
+        <v>0.884999990463257</v>
+      </c>
+      <c r="D820" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E820" t="n">
+        <v>0.839999973773956</v>
+      </c>
+      <c r="F820" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="G820" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="H820" t="n">
+        <v>31000</v>
+      </c>
+      <c r="I820" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24158,6 +24158,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="821">
+      <c r="A821" t="s">
+        <v>9</v>
+      </c>
+      <c r="B821" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C821" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D821" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E821" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="F821" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="G821" t="n">
+        <v>0.865000009536743</v>
+      </c>
+      <c r="H821" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I821" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EXEC.MI.xlsx
+++ b/data/EXEC.MI.xlsx
@@ -24187,6 +24187,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="s">
+        <v>9</v>
+      </c>
+      <c r="B822" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C822" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="D822" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="E822" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="F822" t="n">
+        <v>0.839999973773956</v>
+      </c>
+      <c r="G822" t="n">
+        <v>0.839999973773956</v>
+      </c>
+      <c r="H822" t="n">
+        <v>34000</v>
+      </c>
+      <c r="I822" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
